--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="147">
   <si>
     <t>Mat</t>
   </si>
@@ -46,6 +46,18 @@
     <t>TEMAS DE FÍSICA</t>
   </si>
   <si>
+    <t>6AEM</t>
+  </si>
+  <si>
+    <t>6APM</t>
+  </si>
+  <si>
+    <t>6BEM</t>
+  </si>
+  <si>
+    <t>6AEV</t>
+  </si>
+  <si>
     <t>6APV</t>
   </si>
   <si>
@@ -70,6 +82,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
@@ -97,6 +115,72 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>COLOTL</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>OJEDA</t>
   </si>
   <si>
@@ -106,33 +190,96 @@
     <t>IBAÑEZ</t>
   </si>
   <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
     <t>CARRASCO</t>
   </si>
   <si>
@@ -142,7 +289,28 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
   </si>
   <si>
     <t>IVETTE</t>
@@ -172,6 +340,87 @@
     <t>DORA LUZ</t>
   </si>
   <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ALMA RUBI</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>ESTEFANI</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>OMAR ALDAIR</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>ANGELA MONTSERRAT</t>
+  </si>
+  <si>
     <t>KARLA RENATA</t>
   </si>
   <si>
@@ -182,6 +431,33 @@
   </si>
   <si>
     <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -539,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -579,19 +855,19 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>41.18</v>
+        <v>46.67</v>
       </c>
       <c r="H2">
         <v>6.1</v>
@@ -605,21 +881,125 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="G3">
+      <c r="C4">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>32.14</v>
+      </c>
+      <c r="H4">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>42.86</v>
+      </c>
+      <c r="H5">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>41.18</v>
+      </c>
+      <c r="H6">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
         <v>57.89</v>
       </c>
-      <c r="H3">
+      <c r="H7">
         <v>5.9</v>
       </c>
     </row>
@@ -630,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -670,13 +1050,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -693,18 +1073,110 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>0</v>
       </c>
     </row>
@@ -715,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -755,19 +1227,19 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>41.18</v>
+        <v>46.67</v>
       </c>
       <c r="H2">
         <v>6.3</v>
@@ -781,21 +1253,125 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="G3">
+      <c r="C4">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>32.14</v>
+      </c>
+      <c r="H4">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>42.86</v>
+      </c>
+      <c r="H5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>41.18</v>
+      </c>
+      <c r="H6">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+      <c r="G7">
         <v>57.89</v>
       </c>
-      <c r="H3">
+      <c r="H7">
         <v>6.2</v>
       </c>
     </row>
@@ -806,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -815,39 +1391,39 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920260</v>
+        <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -861,16 +1437,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920270</v>
+        <v>20330051920021</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -884,22 +1460,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920272</v>
+        <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -907,22 +1483,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920238</v>
+        <v>20330051920270</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -930,22 +1506,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920278</v>
+        <v>20330051920272</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -953,22 +1529,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920317</v>
+        <v>19330051920238</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -976,22 +1552,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920322</v>
+        <v>20330051920278</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -999,22 +1575,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920326</v>
+        <v>20330051920317</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1022,22 +1598,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920335</v>
+        <v>20330051920322</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1045,93 +1621,990 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920271</v>
+        <v>20330051920326</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920276</v>
+        <v>20330051920335</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920241</v>
+        <v>20330051920039</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>20330051920040</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920046</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920365</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920097</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920058</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920112</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920361</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920003</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920007</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920014</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920028</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920029</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920033</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920034</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920037</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920068</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920337</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" t="s">
+        <v>124</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920341</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920381</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920347</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920349</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920350</v>
+      </c>
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>20330051920352</v>
+      </c>
+      <c r="B36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>19330050470596</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920356</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920357</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920383</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" t="s">
+        <v>133</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920271</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" t="s">
+        <v>134</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>20330051920276</v>
+      </c>
+      <c r="B42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>19330051920241</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
         <v>20330051920397</v>
       </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>20330051920044</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>20330051920045</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>20330051920048</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" t="s">
+        <v>140</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>20330051920052</v>
+      </c>
+      <c r="B48" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>20330051920057</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" t="s">
+        <v>142</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>20330051920096</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" t="s">
+        <v>143</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>20330051920102</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" t="s">
+        <v>144</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>20330051920107</v>
+      </c>
+      <c r="B52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>20330051920113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" t="s">
+        <v>146</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="140">
   <si>
     <t>Mat</t>
   </si>
@@ -82,229 +82,223 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>APALE</t>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>CHONCOA</t>
   </si>
   <si>
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
+    <t>JOSUE</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
@@ -313,126 +307,126 @@
     <t>OCTAVIO</t>
   </si>
   <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>ESTEFANI</t>
+  </si>
+  <si>
+    <t>OMAR ALDAIR</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>ANGELA MONTSERRAT</t>
+  </si>
+  <si>
     <t>IVETTE</t>
   </si>
   <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>DANTE GAMALIEL</t>
   </si>
   <si>
     <t>MARCOS</t>
   </si>
   <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
     <t>JESUS ANTONIO</t>
   </si>
   <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ALMA RUBI</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>ESTEFANI</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>DANTE GAMALIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>URIEL</t>
   </si>
   <si>
@@ -440,21 +434,6 @@
   </si>
   <si>
     <t>DAVID</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
   </si>
   <si>
     <t>ALEXANDER</t>
@@ -1053,16 +1032,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>53.33</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1076,16 +1058,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1099,16 +1084,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>53.57</v>
+      </c>
+      <c r="H4">
+        <v>5.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1122,16 +1110,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H5">
+        <v>5.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1145,16 +1136,19 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>35.29</v>
+      </c>
+      <c r="H6">
+        <v>6.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1168,16 +1162,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>57.89</v>
+      </c>
+      <c r="H7">
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -1233,16 +1230,16 @@
         <v>0</v>
       </c>
       <c r="E2">
+        <v>14</v>
+      </c>
+      <c r="F2">
         <v>16</v>
       </c>
-      <c r="F2">
-        <v>14</v>
-      </c>
       <c r="G2">
-        <v>46.67</v>
+        <v>53.33</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1259,16 +1256,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1285,16 +1282,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>32.14</v>
+        <v>53.57</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1311,16 +1308,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1337,16 +1334,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>41.18</v>
+        <v>35.29</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1372,7 +1369,7 @@
         <v>57.89</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1382,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1414,7 +1411,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920013</v>
+        <v>20330051920362</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1423,7 +1420,7 @@
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1437,7 +1434,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920021</v>
+        <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1446,7 +1443,7 @@
         <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1460,7 +1457,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920260</v>
+        <v>20330051920021</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1469,13 +1466,13 @@
         <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1483,22 +1480,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920270</v>
+        <v>20330051920060</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1506,22 +1503,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920272</v>
+        <v>20330051920087</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1529,22 +1526,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920238</v>
+        <v>20330051920061</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1552,22 +1549,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920278</v>
+        <v>20330051920063</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1575,22 +1572,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920317</v>
+        <v>20330051920270</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1598,22 +1595,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920322</v>
+        <v>20330051920272</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1621,22 +1618,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920326</v>
+        <v>20330051920273</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1644,22 +1641,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920335</v>
+        <v>19330051920238</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1667,22 +1664,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920039</v>
+        <v>20330051920278</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1690,7 +1687,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920040</v>
+        <v>20330051920335</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
@@ -1699,13 +1696,13 @@
         <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1713,7 +1710,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920046</v>
+        <v>20330051920040</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1722,7 +1719,7 @@
         <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1736,16 +1733,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920365</v>
+        <v>20330051920046</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1759,16 +1756,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920097</v>
+        <v>20330051920365</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1782,7 +1779,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920058</v>
+        <v>20330051920097</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -1791,7 +1788,7 @@
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1805,7 +1802,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920112</v>
+        <v>20330051920111</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -1814,7 +1811,7 @@
         <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1828,39 +1825,39 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920361</v>
+        <v>20330051920112</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920003</v>
+        <v>20330051920361</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1874,16 +1871,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920007</v>
+        <v>20330051920003</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1897,16 +1894,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920014</v>
+        <v>20330051920011</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
         <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1920,16 +1917,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920028</v>
+        <v>20330051920012</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1943,16 +1940,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920029</v>
+        <v>20330051920028</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1966,16 +1963,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920033</v>
+        <v>20330051920029</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1989,16 +1986,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920034</v>
+        <v>20330051920033</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2012,22 +2009,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920037</v>
+        <v>20330051920068</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2035,22 +2032,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920068</v>
+        <v>20330051920341</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2058,16 +2055,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920337</v>
+        <v>20330051920381</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2081,16 +2078,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920341</v>
+        <v>20330051920347</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2104,16 +2101,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920381</v>
+        <v>20330051920349</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2127,16 +2124,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920347</v>
+        <v>20330051920350</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2150,16 +2147,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920349</v>
+        <v>19330050470596</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2173,16 +2170,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920350</v>
+        <v>20330051920356</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2196,16 +2193,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920352</v>
+        <v>20330051920357</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
         <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2219,16 +2216,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330050470596</v>
+        <v>20330051920383</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2242,22 +2239,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920356</v>
+        <v>20330051920260</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2265,22 +2262,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920357</v>
+        <v>20330051920271</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2288,22 +2285,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>20330051920383</v>
+        <v>19220030050208</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2311,16 +2308,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>20330051920271</v>
+        <v>20330051920276</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
         <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2334,16 +2331,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>20330051920276</v>
+        <v>19330051920241</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
         <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2357,22 +2354,22 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920241</v>
+        <v>20330051920322</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2383,13 +2380,13 @@
         <v>20330051920397</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2403,22 +2400,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>20330051920044</v>
+        <v>20330051920326</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C45" t="s">
         <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2426,16 +2423,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>20330051920045</v>
+        <v>20330051920044</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
         <v>91</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2449,16 +2446,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>20330051920048</v>
+        <v>20330051920045</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2472,16 +2469,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>20330051920052</v>
+        <v>20330051920048</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2495,16 +2492,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>20330051920057</v>
+        <v>20330051920113</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2513,98 +2510,6 @@
         <v>11</v>
       </c>
       <c r="G49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>20330051920096</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" t="s">
-        <v>94</v>
-      </c>
-      <c r="D50" t="s">
-        <v>143</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>20330051920102</v>
-      </c>
-      <c r="B51" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" t="s">
-        <v>144</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>20330051920107</v>
-      </c>
-      <c r="B52" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D52" t="s">
-        <v>145</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>11</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>20330051920113</v>
-      </c>
-      <c r="B53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" t="s">
-        <v>146</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>11</v>
-      </c>
-      <c r="G53">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
@@ -94,6 +94,9 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
@@ -109,135 +112,132 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
     <t>EVARISTO</t>
   </si>
   <si>
@@ -310,6 +310,9 @@
     <t>ANGEL SAID</t>
   </si>
   <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
@@ -325,91 +328,88 @@
     <t>MIGUEL ANGEL ONAM</t>
   </si>
   <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>ESTEFANI</t>
+  </si>
+  <si>
+    <t>OMAR ALDAIR</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>ANGELA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
     <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>ESTEFANI</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
   </si>
   <si>
     <t>KAREN YAZMIN</t>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920087</v>
+        <v>19330051920051</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>97</v>
@@ -1526,13 +1526,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
         <v>98</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920063</v>
+        <v>20330051920061</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
         <v>99</v>
@@ -1572,13 +1572,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920270</v>
+        <v>20330051920063</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
         <v>100</v>
@@ -1587,7 +1587,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1595,13 +1595,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920272</v>
+        <v>20330051920270</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>101</v>
@@ -1618,13 +1618,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920273</v>
+        <v>20330051920272</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
         <v>102</v>
@@ -1670,7 +1670,7 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
         <v>104</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920335</v>
+        <v>20330051920040</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
@@ -1702,7 +1702,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920040</v>
+        <v>20330051920046</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1733,7 +1733,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920046</v>
+        <v>20330051920365</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
@@ -1756,13 +1756,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920365</v>
+        <v>20330051920097</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
         <v>108</v>
@@ -1779,13 +1779,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920097</v>
+        <v>20330051920111</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
         <v>109</v>
@@ -1802,13 +1802,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920111</v>
+        <v>20330051920112</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
         <v>110</v>
@@ -1825,13 +1825,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920112</v>
+        <v>20330051920361</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>111</v>
@@ -1840,21 +1840,21 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920361</v>
+        <v>20330051920003</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
         <v>112</v>
@@ -1871,13 +1871,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920003</v>
+        <v>20330051920011</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
         <v>113</v>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920011</v>
+        <v>20330051920012</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
         <v>77</v>
@@ -1917,13 +1917,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920012</v>
+        <v>20330051920028</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920028</v>
+        <v>20330051920029</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
         <v>116</v>
@@ -1963,13 +1963,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920029</v>
+        <v>20330051920033</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
         <v>117</v>
@@ -1986,13 +1986,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920033</v>
+        <v>20330051920068</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
         <v>118</v>
@@ -2001,7 +2001,7 @@
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2009,13 +2009,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920068</v>
+        <v>20330051920341</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
         <v>119</v>
@@ -2024,7 +2024,7 @@
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2032,13 +2032,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920341</v>
+        <v>20330051920381</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
         <v>120</v>
@@ -2055,13 +2055,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920381</v>
+        <v>20330051920347</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -2078,13 +2078,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920347</v>
+        <v>20330051920349</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
         <v>122</v>
@@ -2101,13 +2101,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920349</v>
+        <v>20330051920350</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
         <v>123</v>
@@ -2124,13 +2124,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920350</v>
+        <v>19330050470596</v>
       </c>
       <c r="B33" t="s">
         <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
         <v>124</v>
@@ -2147,13 +2147,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>19330050470596</v>
+        <v>20330051920356</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
         <v>125</v>
@@ -2170,16 +2170,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920356</v>
+        <v>20330051920357</v>
       </c>
       <c r="B35" t="s">
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2193,16 +2193,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920357</v>
+        <v>20330051920383</v>
       </c>
       <c r="B36" t="s">
         <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2216,13 +2216,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920383</v>
+        <v>20330051920260</v>
       </c>
       <c r="B37" t="s">
         <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
         <v>127</v>
@@ -2231,7 +2231,7 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2239,13 +2239,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920260</v>
+        <v>20330051920271</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
         <v>128</v>
@@ -2262,13 +2262,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920271</v>
+        <v>19220030050208</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
         <v>129</v>
@@ -2285,13 +2285,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>19220030050208</v>
+        <v>20330051920273</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
         <v>130</v>
@@ -2403,7 +2403,7 @@
         <v>20330051920326</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
         <v>90</v>
@@ -2495,10 +2495,10 @@
         <v>20330051920113</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
         <v>139</v>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
@@ -88,63 +88,63 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
@@ -211,48 +211,48 @@
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -304,64 +304,64 @@
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
     <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920021</v>
+        <v>20330051920060</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1480,13 +1480,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920060</v>
+        <v>19330051920051</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>96</v>
@@ -1495,7 +1495,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920051</v>
+        <v>20330051920087</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>97</v>
@@ -1526,13 +1526,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920087</v>
+        <v>20330051920061</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
         <v>98</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920061</v>
+        <v>20330051920063</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1572,13 +1572,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920063</v>
+        <v>20330051920270</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>100</v>
@@ -1587,7 +1587,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1595,13 +1595,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920270</v>
+        <v>20330051920272</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
         <v>101</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920272</v>
+        <v>19330051920238</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
@@ -1641,13 +1641,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920238</v>
+        <v>20330051920278</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
         <v>103</v>
@@ -1664,13 +1664,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920278</v>
+        <v>20330051920040</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
         <v>104</v>
@@ -1679,7 +1679,7 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920040</v>
+        <v>20330051920046</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920046</v>
+        <v>20330051920365</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1733,7 +1733,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920365</v>
+        <v>20330051920097</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920097</v>
+        <v>20330051920111</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -1779,13 +1779,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920111</v>
+        <v>20330051920112</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
         <v>109</v>
@@ -1802,13 +1802,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920112</v>
+        <v>20330051920361</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
         <v>110</v>
@@ -1817,15 +1817,15 @@
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920361</v>
+        <v>20330051920003</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920003</v>
+        <v>20330051920011</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
@@ -1871,13 +1871,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920011</v>
+        <v>20330051920012</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>113</v>
@@ -1894,7 +1894,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920012</v>
+        <v>20330051920021</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -1923,7 +1923,7 @@
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -1946,7 +1946,7 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
         <v>116</v>
@@ -2035,10 +2035,10 @@
         <v>20330051920381</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
         <v>120</v>
@@ -2058,10 +2058,10 @@
         <v>20330051920347</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -2107,7 +2107,7 @@
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
         <v>123</v>
@@ -2242,7 +2242,7 @@
         <v>20330051920271</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
         <v>85</v>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
   <si>
     <t>Mat</t>
   </si>
@@ -82,220 +82,85 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
+    <t>MARCOS SURIEL</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
   </si>
   <si>
     <t>JOSUE</t>
@@ -304,139 +169,28 @@
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
     <t>ANGEL SAID</t>
   </si>
   <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
     <t>MARCO JOSAFAT</t>
   </si>
   <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>ESTEFANI</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ANGELA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>DANTE GAMALIEL</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
     <t>JESUS ANTONIO</t>
   </si>
   <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>JESUS JOAN</t>
   </si>
 </sst>
 </file>
@@ -1230,16 +984,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>53.33</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1256,16 +1010,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1282,16 +1036,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>53.57</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1308,16 +1062,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>33.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1334,16 +1088,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>35.29</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1360,13 +1114,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>57.89</v>
+        <v>68.42</v>
       </c>
       <c r="H7">
         <v>6.6</v>
@@ -1379,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1411,16 +1165,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920362</v>
+        <v>20330051920035</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1434,22 +1188,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920013</v>
+        <v>20330051920354</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1457,22 +1211,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920060</v>
+        <v>19330051920238</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1480,131 +1234,131 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920051</v>
+        <v>20330051920362</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920087</v>
+        <v>20330051920013</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920061</v>
+        <v>20330051920016</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920063</v>
+        <v>20330051920025</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920270</v>
+        <v>20330051920060</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920272</v>
+        <v>20330051920278</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1613,903 +1367,98 @@
         <v>13</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920238</v>
+        <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920278</v>
+        <v>20330051920326</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920040</v>
+        <v>20330051920329</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920046</v>
+        <v>19330051920408</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920365</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920097</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920111</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920112</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920361</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920003</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920011</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920012</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920021</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920028</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920029</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920033</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920068</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920341</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920381</v>
-      </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920347</v>
-      </c>
-      <c r="B30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920349</v>
-      </c>
-      <c r="B31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920350</v>
-      </c>
-      <c r="B32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>19330050470596</v>
-      </c>
-      <c r="B33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920356</v>
-      </c>
-      <c r="B34" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" t="s">
-        <v>125</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920357</v>
-      </c>
-      <c r="B35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920383</v>
-      </c>
-      <c r="B36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920260</v>
-      </c>
-      <c r="B37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" t="s">
-        <v>127</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920271</v>
-      </c>
-      <c r="B38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>19220030050208</v>
-      </c>
-      <c r="B39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" t="s">
-        <v>129</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>20330051920273</v>
-      </c>
-      <c r="B40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>20330051920276</v>
-      </c>
-      <c r="B41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>19330051920241</v>
-      </c>
-      <c r="B42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>20330051920322</v>
-      </c>
-      <c r="B43" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>20330051920397</v>
-      </c>
-      <c r="B44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>20330051920326</v>
-      </c>
-      <c r="B45" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>20330051920044</v>
-      </c>
-      <c r="B46" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>20330051920045</v>
-      </c>
-      <c r="B47" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" t="s">
-        <v>137</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>20330051920048</v>
-      </c>
-      <c r="B48" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" t="s">
-        <v>78</v>
-      </c>
-      <c r="D48" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>20330051920113</v>
-      </c>
-      <c r="B49" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" t="s">
-        <v>139</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -88,9 +88,6 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
     <t>HERRERA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -158,9 +152,6 @@
   </si>
   <si>
     <t>JAHEL</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
   </si>
   <si>
     <t>JOSUE</t>
@@ -1133,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,10 +1162,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1194,10 +1185,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1211,39 +1202,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920238</v>
+        <v>20330051920362</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920362</v>
+        <v>20330051920013</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1257,16 +1248,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920013</v>
+        <v>20330051920016</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1280,16 +1271,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920016</v>
+        <v>20330051920025</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1303,16 +1294,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920025</v>
+        <v>20330051920060</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1326,22 +1317,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920060</v>
+        <v>20330051920278</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1349,22 +1340,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920278</v>
+        <v>20330051920397</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1372,16 +1363,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920397</v>
+        <v>20330051920326</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1395,16 +1386,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1418,16 +1409,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920329</v>
+        <v>19330051920408</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1436,29 +1427,6 @@
         <v>14</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920408</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>HERRERA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -152,6 +158,9 @@
   </si>
   <si>
     <t>JAHEL</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
   </si>
   <si>
     <t>JOSUE</t>
@@ -1053,16 +1062,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>85.70999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1124,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1162,10 +1171,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1185,10 +1194,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1202,39 +1211,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920362</v>
+        <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920013</v>
+        <v>20330051920362</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1248,16 +1257,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920016</v>
+        <v>20330051920013</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1271,16 +1280,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920025</v>
+        <v>20330051920016</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1294,16 +1303,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920060</v>
+        <v>20330051920025</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1317,22 +1326,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920278</v>
+        <v>20330051920060</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1340,22 +1349,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920397</v>
+        <v>20330051920278</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1363,16 +1372,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920326</v>
+        <v>20330051920397</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1386,16 +1395,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920329</v>
+        <v>20330051920326</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1409,16 +1418,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920408</v>
+        <v>20330051920329</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1427,6 +1436,29 @@
         <v>14</v>
       </c>
       <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920408</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>
